--- a/data_u1/studies_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/studies_2025-08-15_LSR3_H.xlsx
@@ -1275,7 +1275,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Efficacy, dropouts</t>
+          <t>Efficacy, dropouts, side-effects</t>
         </is>
       </c>
       <c r="O12">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SEP361-108, NCT05015673</t>
+          <t>SEP361-108 , NCT05015673</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Efficacy, dropouts</t>
+          <t>Efficacy, dropouts, side-effects</t>
         </is>
       </c>
       <c r="O18">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SEP361-124, NCT05402111</t>
+          <t>SEP361-124, NCT05402111 (2022)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">

--- a/data_u1/studies_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/studies_2025-08-15_LSR3_H.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BP30134, NCT02699372</t>
+          <t>BP30134, NCT02699372, 2015-005509-35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/data_u1/studies_2025-08-15_LSR3_H.xlsx
+++ b/data_u1/studies_2025-08-15_LSR3_H.xlsx
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="H18">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="R18">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19">
